--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6037735849056604</v>
+        <v>0.559322033898305</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3546099290780142</v>
+        <v>0.3450704225352113</v>
       </c>
       <c r="D2">
-        <v>0.7398373983739838</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="E2">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
